--- a/public/sap-reporting/expansion-150-downloads/EXT-FI20-01.xlsx
+++ b/public/sap-reporting/expansion-150-downloads/EXT-FI20-01.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R737e14a249af495d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="R1d62fabfaeda4af0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R88d9c9db134549ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Layout" sheetId="1" r:id="R1bae12c3559d4f3b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Flat input" sheetId="2" r:id="Ra2aae57c04f44455"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fields" sheetId="3" r:id="R811aaaa007da4d4b"/>
   </x:sheets>
 </x:workbook>
 </file>
